--- a/output/pdf_financials_xlsx/TVE.xlsx
+++ b/output/pdf_financials_xlsx/TVE.xlsx
@@ -2130,37 +2130,37 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>18.900843</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>25.244853</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>47.828039</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>59.547184</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.065427</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>148.649</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>177.576</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>167.311</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.120658</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.212337</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>377.683</v>
+        <v>0.377683</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>631.063</v>
@@ -2188,13 +2188,13 @@
         <v>-6443.402</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.64183</v>
+        <v>14.259013</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>16.696408</v>
+        <v>41.941261</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-31.126159</v>
+        <v>16.70188</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2207,22 +2207,22 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-17.535</v>
+        <v>131.114</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>59.142</v>
+        <v>236.718</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-53.409</v>
+        <v>113.902</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.398928</v>
+        <v>-0.27827</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.519766</v>
+        <v>0.7321029999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>822.3680000000001</v>
+        <v>445.062683</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>772.42</v>
@@ -2250,13 +2250,13 @@
         <v>-100.1655122882808</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-13.62893967340846</v>
+        <v>41.8660803991846</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>28.80177255604879</v>
+        <v>72.34985273694076</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-26.18698842783492</v>
+        <v>14.05158722870649</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2269,22 +2269,22 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-6.623454621686856</v>
+        <v>49.52538518778731</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>16.03837799285701</v>
+        <v>64.19418960659303</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-17.36911939745166</v>
+        <v>37.04202358420002</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-201.9551163603043</v>
+        <v>-140.8726643143171</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>86.78402254728937</v>
+        <v>122.2373977115436</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>69.69066783274268</v>
+        <v>37.71634548730282</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>54.919013616349</v>
@@ -6462,37 +6462,37 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>18.900843</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>25.244853</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>47.828039</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>59.547184</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.065427</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>148.649</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>177.576</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>167.311</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.120658</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.212337</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.377683</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
@@ -24274,7 +24274,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -30650,7 +30650,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -35844,7 +35844,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -47768,7 +47768,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -49475,7 +49475,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -51090,7 +51090,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -52056,7 +52056,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">

--- a/output/pdf_financials_xlsx/TVE.xlsx
+++ b/output/pdf_financials_xlsx/TVE.xlsx
@@ -937,7 +937,7 @@
         <v>0.128284</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.281207</v>
+        <v>282.276</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>309.611</v>
@@ -995,7 +995,7 @@
         <v>-0.032438</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>264.459793</v>
+        <v>-17.535</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>59.142</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08424</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008736000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.260364</v>
+        <v>-2.344604</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.771278</v>
+        <v>-4.780014</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-6443.402</v>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.260364</v>
+        <v>-2.344604</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.771278</v>
+        <v>-4.780014</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-6443.402</v>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-26.50560421169548</v>
+        <v>-27.49342391630644</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-0.1224786740113651</v>
+        <v>-0.1227029270723193</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-100.1655122882808</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>7.391</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>5.444</v>
       </c>
     </row>
     <row r="35">
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>7.391</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>5.444</v>
       </c>
     </row>
     <row r="37">
@@ -3288,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>56.336</v>
+        <v>54.116</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>76.185</v>
+        <v>68.794</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>50.392</v>
+        <v>44.948</v>
       </c>
     </row>
     <row r="49">
@@ -7886,10 +7886,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-132.083</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-351.598</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-132.083</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-351.598</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -22840,7 +22840,11 @@
           <t>Repayment of indebtedness 7</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -43858,7 +43862,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -51191,7 +51195,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -54133,7 +54137,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" s="5" t="n">

--- a/output/pdf_financials_xlsx/TVE.xlsx
+++ b/output/pdf_financials_xlsx/TVE.xlsx
@@ -7158,34 +7158,34 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>31.107281</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>12.247937</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.002198</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>5.301</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>9.888999999999999</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.015525</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.046217</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -30553,7 +30553,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 7 and 8)</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32565,7 +32569,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -34444,7 +34452,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TVE.xlsx
+++ b/output/pdf_financials_xlsx/TVE.xlsx
@@ -1335,28 +1335,28 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>1.883282</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.958798</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.411305</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.004615</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.611</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>20.832</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.398</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.087544</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.129258</v>
@@ -1578,15 +1578,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>18.57969</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-37.084957</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1598,25 +1594,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J20" s="3" t="n">
+        <v>-21.146</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>79.974</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-67.807</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>-0.486472</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>0.390508</v>
@@ -1769,10 +1757,10 @@
         <v>-4.64183</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16.696408</v>
+        <v>18.57969</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-31.126159</v>
+        <v>-37.084957</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1785,16 +1773,16 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-17.535</v>
+        <v>-21.146</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>59.142</v>
+        <v>79.974</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-53.409</v>
+        <v>-67.807</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-0.398928</v>
+        <v>-0.486472</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>0.390508</v>
@@ -2315,10 +2303,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>11.27956384391182</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-19.14401966525969</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -2331,16 +2319,16 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-20.5930995152552</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>35.22369889418687</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-26.95800333277163</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-21.9448120964184</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>24.86849851664018</v>
@@ -2377,10 +2365,10 @@
         <v>-13.62893967340846</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>28.80177255604879</v>
+        <v>32.05048687968659</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-26.18698842783492</v>
+        <v>-31.20023064219892</v>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
@@ -2393,16 +2381,16 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-6.623454621686856</v>
+        <v>-7.987429223278601</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>16.03837799285701</v>
+        <v>21.68768796457249</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-17.36911939745166</v>
+        <v>-22.05148718348976</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>-201.9551163603043</v>
+        <v>-246.2737871646763</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>65.20213918743603</v>
@@ -4654,16 +4642,16 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>2.209</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.002484</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.004479</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
@@ -4712,16 +4700,16 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>2.209</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.002484</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.004479</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4944,16 +4932,16 @@
         <v>2.391</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>9.592000000000001</v>
+        <v>7.383</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.020023</v>
+        <v>0.017539</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.022336</v>
+        <v>0.018736</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>299.096</v>
+        <v>299.091521</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>173.839</v>
@@ -5253,25 +5241,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.002854835061871991</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.004875195773260219</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.00285572632622707</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>2.070506310213527e-06</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -6403,10 +6383,10 @@
         <v>-4.64183</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>16.696408</v>
+        <v>18.57969</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-31.126159</v>
+        <v>-37.084957</v>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
@@ -6419,16 +6399,16 @@
         </is>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-17.535</v>
+        <v>-21.146</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>59.142</v>
+        <v>79.974</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-53.409</v>
+        <v>-67.807</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-0.398928</v>
+        <v>-0.486472</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>0.390508</v>
@@ -6801,7 +6781,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.241235</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-730.98</v>
@@ -12413,7 +12393,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -14476,7 +14460,11 @@
           <t>Lease liabilities (note 12)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -18575,7 +18563,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -18773,7 +18765,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -22143,7 +22139,11 @@
           <t>Deferred income tax expense (recovery) 12</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -29052,7 +29052,11 @@
           <t>Deferred income tax expense (recovery) (note 15)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -33458,7 +33462,11 @@
           <t>Deferred income tax expense (recovery) (note 14)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -35256,7 +35264,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -36533,7 +36545,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37889,7 +37905,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -40307,7 +40327,11 @@
           <t>Changes in non-cash operating working capital (note 13)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>-0.241235</v>
       </c>
@@ -43084,7 +43108,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -49980,7 +50008,11 @@
           <t>Deferred income tax recovery (expense) (note 15)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -50643,7 +50675,11 @@
           <t>Deferred income tax recovery (expense) (note 14)</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -51876,7 +51912,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
